--- a/results_article/MSO.xlsx
+++ b/results_article/MSO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr codeName="Ten_skoroszyt" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakto\Desktop\Pulpit\FaultDiagnosis\FaultDiagnosis\results_article\mso_conflicts_diagnoses\csv\MSO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakto\Desktop\Pulpit\FaultDiagnosis\FaultDiagnosis\results_article\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5492BAF6-94C2-41A8-825C-DE60BE1B15E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D03ECA-8CC2-4290-97D1-6E1233D3A860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="802" xr2:uid="{D7477BF9-CFC4-44C8-A16A-B837FBE23178}"/>
+    <workbookView xWindow="-28920" yWindow="-90" windowWidth="29040" windowHeight="15840" tabRatio="802" xr2:uid="{D7477BF9-CFC4-44C8-A16A-B837FBE23178}"/>
   </bookViews>
   <sheets>
     <sheet name="MSO" sheetId="1" r:id="rId1"/>
@@ -1322,15 +1322,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="14" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1437,6 +1428,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1889,466 +1889,466 @@
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="2:65" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="17" t="s">
+      <c r="C2" s="54"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="17" t="s">
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="17" t="s">
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-      <c r="V2" s="19"/>
-      <c r="W2" s="17" t="s">
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="19"/>
-      <c r="AC2" s="17" t="s">
+      <c r="X2" s="54"/>
+      <c r="Y2" s="54"/>
+      <c r="Z2" s="54"/>
+      <c r="AA2" s="54"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="AD2" s="18"/>
-      <c r="AE2" s="18"/>
-      <c r="AF2" s="18"/>
-      <c r="AG2" s="18"/>
-      <c r="AH2" s="19"/>
-      <c r="AI2" s="17" t="s">
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="54"/>
+      <c r="AF2" s="54"/>
+      <c r="AG2" s="54"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="AJ2" s="18"/>
-      <c r="AK2" s="18"/>
-      <c r="AL2" s="18"/>
-      <c r="AM2" s="18"/>
-      <c r="AN2" s="19"/>
-      <c r="AO2" s="17" t="s">
+      <c r="AJ2" s="54"/>
+      <c r="AK2" s="54"/>
+      <c r="AL2" s="54"/>
+      <c r="AM2" s="54"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="AP2" s="18"/>
-      <c r="AQ2" s="18"/>
-      <c r="AR2" s="18"/>
-      <c r="AS2" s="18"/>
-      <c r="AT2" s="19"/>
-      <c r="AU2" s="17" t="s">
+      <c r="AP2" s="54"/>
+      <c r="AQ2" s="54"/>
+      <c r="AR2" s="54"/>
+      <c r="AS2" s="54"/>
+      <c r="AT2" s="55"/>
+      <c r="AU2" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="AV2" s="18"/>
-      <c r="AW2" s="18"/>
-      <c r="AX2" s="18"/>
-      <c r="AY2" s="18"/>
-      <c r="AZ2" s="19"/>
-      <c r="BA2" s="17" t="s">
+      <c r="AV2" s="54"/>
+      <c r="AW2" s="54"/>
+      <c r="AX2" s="54"/>
+      <c r="AY2" s="54"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="BB2" s="18"/>
-      <c r="BC2" s="18"/>
-      <c r="BD2" s="18"/>
-      <c r="BE2" s="18"/>
-      <c r="BF2" s="19"/>
-      <c r="BG2" s="17" t="s">
+      <c r="BB2" s="54"/>
+      <c r="BC2" s="54"/>
+      <c r="BD2" s="54"/>
+      <c r="BE2" s="54"/>
+      <c r="BF2" s="55"/>
+      <c r="BG2" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="BH2" s="18"/>
-      <c r="BI2" s="18"/>
-      <c r="BJ2" s="18"/>
-      <c r="BK2" s="18"/>
-      <c r="BL2" s="19"/>
+      <c r="BH2" s="54"/>
+      <c r="BI2" s="54"/>
+      <c r="BJ2" s="54"/>
+      <c r="BK2" s="54"/>
+      <c r="BL2" s="55"/>
     </row>
     <row r="3" spans="2:65" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="J3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="L3" s="24" t="s">
+      <c r="L3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="N3" s="24" t="s">
+      <c r="N3" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="O3" s="25" t="s">
+      <c r="O3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="P3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="Q3" s="23" t="s">
+      <c r="Q3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="R3" s="24" t="s">
+      <c r="R3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="S3" s="24" t="s">
+      <c r="S3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="T3" s="24" t="s">
+      <c r="T3" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="U3" s="25" t="s">
+      <c r="U3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="V3" s="26" t="s">
+      <c r="V3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="W3" s="23" t="s">
+      <c r="W3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="X3" s="24" t="s">
+      <c r="X3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="Y3" s="24" t="s">
+      <c r="Y3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="Z3" s="24" t="s">
+      <c r="Z3" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="AA3" s="25" t="s">
+      <c r="AA3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="AB3" s="26" t="s">
+      <c r="AB3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="AC3" s="23" t="s">
+      <c r="AC3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="AD3" s="24" t="s">
+      <c r="AD3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="AE3" s="24" t="s">
+      <c r="AE3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="AF3" s="24" t="s">
+      <c r="AF3" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="AG3" s="25" t="s">
+      <c r="AG3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="AH3" s="26" t="s">
+      <c r="AH3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="AI3" s="23" t="s">
+      <c r="AI3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="AJ3" s="24" t="s">
+      <c r="AJ3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="AK3" s="24" t="s">
+      <c r="AK3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="AL3" s="24" t="s">
+      <c r="AL3" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="AM3" s="25" t="s">
+      <c r="AM3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="AN3" s="26" t="s">
+      <c r="AN3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="AO3" s="23" t="s">
+      <c r="AO3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="AP3" s="24" t="s">
+      <c r="AP3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="AQ3" s="24" t="s">
+      <c r="AQ3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="AR3" s="24" t="s">
+      <c r="AR3" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="AS3" s="25" t="s">
+      <c r="AS3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="AT3" s="26" t="s">
+      <c r="AT3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="AU3" s="23" t="s">
+      <c r="AU3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="AV3" s="24" t="s">
+      <c r="AV3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="AW3" s="24" t="s">
+      <c r="AW3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="AX3" s="24" t="s">
+      <c r="AX3" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="AY3" s="25" t="s">
+      <c r="AY3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="AZ3" s="26" t="s">
+      <c r="AZ3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="BA3" s="23" t="s">
+      <c r="BA3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="BB3" s="24" t="s">
+      <c r="BB3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="BC3" s="24" t="s">
+      <c r="BC3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="BD3" s="24" t="s">
+      <c r="BD3" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="BE3" s="25" t="s">
+      <c r="BE3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="BF3" s="26" t="s">
+      <c r="BF3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="BG3" s="23" t="s">
+      <c r="BG3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="BH3" s="24" t="s">
+      <c r="BH3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="BI3" s="24" t="s">
+      <c r="BI3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="BJ3" s="24" t="s">
+      <c r="BJ3" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="BK3" s="25" t="s">
+      <c r="BK3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="BL3" s="27" t="s">
+      <c r="BL3" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="BM3" s="28" t="s">
+      <c r="BM3" s="25" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="2:65" ht="60" x14ac:dyDescent="0.25">
-      <c r="B4" s="31" t="s">
+    <row r="4" spans="2:65" ht="45" x14ac:dyDescent="0.25">
+      <c r="B4" s="28" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="11">
         <v>3</v>
       </c>
-      <c r="D4" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="36">
+      <c r="D4" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="33">
         <v>3</v>
       </c>
       <c r="F4" s="12">
         <v>3</v>
       </c>
       <c r="G4" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" s="12">
         <v>0</v>
       </c>
-      <c r="I4" s="37">
-        <v>1</v>
-      </c>
-      <c r="J4" s="38" t="s">
+      <c r="I4" s="34">
+        <v>1</v>
+      </c>
+      <c r="J4" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="33">
         <v>3</v>
       </c>
       <c r="L4" s="12">
         <v>3</v>
       </c>
       <c r="M4" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" s="12">
         <v>0</v>
       </c>
-      <c r="O4" s="37">
-        <v>1</v>
-      </c>
-      <c r="P4" s="38" t="s">
+      <c r="O4" s="34">
+        <v>1</v>
+      </c>
+      <c r="P4" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="33">
         <v>3</v>
       </c>
       <c r="R4" s="12">
         <v>3</v>
       </c>
       <c r="S4" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4" s="12">
         <v>0</v>
       </c>
-      <c r="U4" s="37">
-        <v>1</v>
-      </c>
-      <c r="V4" s="38" t="s">
+      <c r="U4" s="34">
+        <v>1</v>
+      </c>
+      <c r="V4" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="W4" s="36">
+      <c r="W4" s="33">
         <v>3</v>
       </c>
       <c r="X4" s="12">
         <v>3</v>
       </c>
       <c r="Y4" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="12">
         <v>0</v>
       </c>
-      <c r="AA4" s="37">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="38" t="s">
+      <c r="AA4" s="34">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="AC4" s="36">
+      <c r="AC4" s="33">
         <v>3</v>
       </c>
       <c r="AD4" s="12">
         <v>3</v>
       </c>
       <c r="AE4" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="12">
         <v>0</v>
       </c>
-      <c r="AG4" s="37">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="38" t="s">
+      <c r="AG4" s="34">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="AI4" s="36">
+      <c r="AI4" s="33">
         <v>3</v>
       </c>
       <c r="AJ4" s="12">
         <v>3</v>
       </c>
       <c r="AK4" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL4" s="12">
         <v>0</v>
       </c>
-      <c r="AM4" s="37">
-        <v>1</v>
-      </c>
-      <c r="AN4" s="38" t="s">
+      <c r="AM4" s="34">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="AO4" s="36">
-        <v>3</v>
+      <c r="AO4" s="33">
+        <v>0</v>
       </c>
       <c r="AP4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" s="12">
         <v>0</v>
       </c>
       <c r="AR4" s="12">
-        <v>1</v>
-      </c>
-      <c r="AS4" s="37">
-        <v>0</v>
-      </c>
-      <c r="AT4" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="AS4" s="34">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="AU4" s="36">
+      <c r="AU4" s="33">
         <v>3</v>
       </c>
       <c r="AV4" s="12">
         <v>3</v>
       </c>
       <c r="AW4" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX4" s="12">
         <v>0</v>
       </c>
-      <c r="AY4" s="37">
-        <v>1</v>
-      </c>
-      <c r="AZ4" s="38" t="s">
+      <c r="AY4" s="34">
+        <v>1</v>
+      </c>
+      <c r="AZ4" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="BA4" s="36">
-        <v>3</v>
+      <c r="BA4" s="33">
+        <v>0</v>
       </c>
       <c r="BB4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC4" s="12">
         <v>0</v>
       </c>
       <c r="BD4" s="12">
-        <v>1</v>
-      </c>
-      <c r="BE4" s="37">
-        <v>0</v>
-      </c>
-      <c r="BF4" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="BE4" s="34">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="BG4" s="40">
+      <c r="BG4" s="37">
         <v>3</v>
       </c>
       <c r="BH4" s="9">
         <v>3</v>
       </c>
       <c r="BI4" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ4" s="9">
         <v>0</v>
@@ -2356,32 +2356,32 @@
       <c r="BK4" s="13">
         <v>1</v>
       </c>
-      <c r="BL4" s="41" t="s">
+      <c r="BL4" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="BM4" s="29">
+      <c r="BM4" s="26">
         <f>AVERAGEA(I4,O4,U4,AA4,AG4,AM4,AS4,AY4,BE4,BK4)</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="2:65" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:65" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C5" s="3">
         <v>2</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="42">
+      <c r="D5" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="39">
         <v>2</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
       </c>
       <c r="G5" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" s="10">
         <v>0</v>
@@ -2389,17 +2389,17 @@
       <c r="I5" s="14">
         <v>1</v>
       </c>
-      <c r="J5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="K5" s="42">
+      <c r="J5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" s="39">
         <v>2</v>
       </c>
       <c r="L5" s="10">
         <v>2</v>
       </c>
       <c r="M5" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N5" s="10">
         <v>0</v>
@@ -2407,17 +2407,17 @@
       <c r="O5" s="14">
         <v>1</v>
       </c>
-      <c r="P5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="42">
+      <c r="P5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="39">
         <v>2</v>
       </c>
       <c r="R5" s="10">
         <v>2</v>
       </c>
       <c r="S5" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T5" s="10">
         <v>0</v>
@@ -2425,17 +2425,17 @@
       <c r="U5" s="14">
         <v>1</v>
       </c>
-      <c r="V5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="W5" s="42">
+      <c r="V5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="W5" s="39">
         <v>2</v>
       </c>
       <c r="X5" s="10">
         <v>2</v>
       </c>
       <c r="Y5" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="10">
         <v>0</v>
@@ -2443,17 +2443,17 @@
       <c r="AA5" s="14">
         <v>1</v>
       </c>
-      <c r="AB5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC5" s="42">
+      <c r="AB5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC5" s="39">
         <v>2</v>
       </c>
       <c r="AD5" s="10">
         <v>2</v>
       </c>
       <c r="AE5" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="10">
         <v>0</v>
@@ -2461,17 +2461,17 @@
       <c r="AG5" s="14">
         <v>1</v>
       </c>
-      <c r="AH5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI5" s="42">
+      <c r="AH5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI5" s="39">
         <v>2</v>
       </c>
       <c r="AJ5" s="10">
         <v>2</v>
       </c>
       <c r="AK5" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL5" s="10">
         <v>0</v>
@@ -2479,35 +2479,35 @@
       <c r="AM5" s="14">
         <v>1</v>
       </c>
-      <c r="AN5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO5" s="42">
-        <v>2</v>
+      <c r="AN5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO5" s="39">
+        <v>0</v>
       </c>
       <c r="AP5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ5" s="10">
         <v>0</v>
       </c>
       <c r="AR5" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS5" s="14">
         <v>0</v>
       </c>
-      <c r="AT5" s="44" t="s">
+      <c r="AT5" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU5" s="42">
+      <c r="AU5" s="39">
         <v>2</v>
       </c>
       <c r="AV5" s="10">
         <v>2</v>
       </c>
       <c r="AW5" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX5" s="10">
         <v>0</v>
@@ -2515,35 +2515,35 @@
       <c r="AY5" s="14">
         <v>1</v>
       </c>
-      <c r="AZ5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="BA5" s="42">
-        <v>2</v>
+      <c r="AZ5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="BA5" s="39">
+        <v>0</v>
       </c>
       <c r="BB5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC5" s="10">
         <v>0</v>
       </c>
       <c r="BD5" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE5" s="14">
         <v>0</v>
       </c>
-      <c r="BF5" s="44" t="s">
+      <c r="BF5" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG5" s="45">
+      <c r="BG5" s="42">
         <v>2</v>
       </c>
       <c r="BH5" s="10">
         <v>2</v>
       </c>
       <c r="BI5" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ5" s="10">
         <v>0</v>
@@ -2551,32 +2551,32 @@
       <c r="BK5" s="14">
         <v>1</v>
       </c>
-      <c r="BL5" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="BM5" s="30">
+      <c r="BL5" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="BM5" s="27">
         <f t="shared" ref="BM5:BM26" si="0">AVERAGEA(I5,O5,U5,AA5,AG5,AM5,AS5,AY5,BE5,BK5)</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="6" spans="2:65" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:65" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C6" s="3">
         <v>2</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="39">
         <v>2</v>
       </c>
       <c r="F6" s="10">
         <v>2</v>
       </c>
       <c r="G6" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" s="10">
         <v>0</v>
@@ -2584,17 +2584,17 @@
       <c r="I6" s="14">
         <v>1</v>
       </c>
-      <c r="J6" s="43" t="s">
+      <c r="J6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="42">
+      <c r="K6" s="39">
         <v>2</v>
       </c>
       <c r="L6" s="10">
         <v>2</v>
       </c>
       <c r="M6" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N6" s="10">
         <v>0</v>
@@ -2602,17 +2602,17 @@
       <c r="O6" s="14">
         <v>1</v>
       </c>
-      <c r="P6" s="43" t="s">
+      <c r="P6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="Q6" s="42">
+      <c r="Q6" s="39">
         <v>2</v>
       </c>
       <c r="R6" s="10">
         <v>2</v>
       </c>
       <c r="S6" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T6" s="10">
         <v>0</v>
@@ -2620,17 +2620,17 @@
       <c r="U6" s="14">
         <v>1</v>
       </c>
-      <c r="V6" s="43" t="s">
+      <c r="V6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="W6" s="42">
+      <c r="W6" s="39">
         <v>2</v>
       </c>
       <c r="X6" s="10">
         <v>2</v>
       </c>
       <c r="Y6" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="10">
         <v>0</v>
@@ -2638,17 +2638,17 @@
       <c r="AA6" s="14">
         <v>1</v>
       </c>
-      <c r="AB6" s="43" t="s">
+      <c r="AB6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="AC6" s="42">
+      <c r="AC6" s="39">
         <v>2</v>
       </c>
       <c r="AD6" s="10">
         <v>2</v>
       </c>
       <c r="AE6" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF6" s="10">
         <v>0</v>
@@ -2656,17 +2656,17 @@
       <c r="AG6" s="14">
         <v>1</v>
       </c>
-      <c r="AH6" s="43" t="s">
+      <c r="AH6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="AI6" s="42">
+      <c r="AI6" s="39">
         <v>2</v>
       </c>
       <c r="AJ6" s="10">
         <v>2</v>
       </c>
       <c r="AK6" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL6" s="10">
         <v>0</v>
@@ -2674,17 +2674,17 @@
       <c r="AM6" s="14">
         <v>1</v>
       </c>
-      <c r="AN6" s="43" t="s">
+      <c r="AN6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="AO6" s="42">
+      <c r="AO6" s="39">
         <v>2</v>
       </c>
       <c r="AP6" s="10">
         <v>2</v>
       </c>
       <c r="AQ6" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR6" s="10">
         <v>0</v>
@@ -2692,17 +2692,17 @@
       <c r="AS6" s="14">
         <v>1</v>
       </c>
-      <c r="AT6" s="43" t="s">
+      <c r="AT6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="AU6" s="42">
+      <c r="AU6" s="39">
         <v>2</v>
       </c>
       <c r="AV6" s="10">
         <v>2</v>
       </c>
       <c r="AW6" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX6" s="10">
         <v>0</v>
@@ -2710,17 +2710,17 @@
       <c r="AY6" s="14">
         <v>1</v>
       </c>
-      <c r="AZ6" s="43" t="s">
+      <c r="AZ6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="BA6" s="42">
+      <c r="BA6" s="39">
         <v>2</v>
       </c>
       <c r="BB6" s="10">
         <v>2</v>
       </c>
       <c r="BC6" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD6" s="10">
         <v>0</v>
@@ -2728,17 +2728,17 @@
       <c r="BE6" s="14">
         <v>1</v>
       </c>
-      <c r="BF6" s="43" t="s">
+      <c r="BF6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="BG6" s="45">
+      <c r="BG6" s="42">
         <v>2</v>
       </c>
       <c r="BH6" s="10">
         <v>2</v>
       </c>
       <c r="BI6" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ6" s="10">
         <v>0</v>
@@ -2746,10 +2746,10 @@
       <c r="BK6" s="14">
         <v>1</v>
       </c>
-      <c r="BL6" s="46" t="s">
+      <c r="BL6" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="BM6" s="30">
+      <c r="BM6" s="27">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2761,17 +2761,17 @@
       <c r="C7" s="3">
         <v>2</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="39">
         <v>2</v>
       </c>
       <c r="F7" s="10">
         <v>2</v>
       </c>
       <c r="G7" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" s="10">
         <v>0</v>
@@ -2779,17 +2779,17 @@
       <c r="I7" s="14">
         <v>1</v>
       </c>
-      <c r="J7" s="43" t="s">
+      <c r="J7" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="42">
+      <c r="K7" s="39">
         <v>2</v>
       </c>
       <c r="L7" s="10">
         <v>2</v>
       </c>
       <c r="M7" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N7" s="10">
         <v>0</v>
@@ -2797,17 +2797,17 @@
       <c r="O7" s="14">
         <v>1</v>
       </c>
-      <c r="P7" s="43" t="s">
+      <c r="P7" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="Q7" s="42">
+      <c r="Q7" s="39">
         <v>2</v>
       </c>
       <c r="R7" s="10">
         <v>2</v>
       </c>
       <c r="S7" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T7" s="10">
         <v>0</v>
@@ -2815,17 +2815,17 @@
       <c r="U7" s="14">
         <v>1</v>
       </c>
-      <c r="V7" s="43" t="s">
+      <c r="V7" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="W7" s="42">
+      <c r="W7" s="39">
         <v>2</v>
       </c>
       <c r="X7" s="10">
         <v>2</v>
       </c>
       <c r="Y7" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="10">
         <v>0</v>
@@ -2833,17 +2833,17 @@
       <c r="AA7" s="14">
         <v>1</v>
       </c>
-      <c r="AB7" s="43" t="s">
+      <c r="AB7" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="AC7" s="42">
+      <c r="AC7" s="39">
         <v>2</v>
       </c>
       <c r="AD7" s="10">
         <v>2</v>
       </c>
       <c r="AE7" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="10">
         <v>0</v>
@@ -2851,17 +2851,17 @@
       <c r="AG7" s="14">
         <v>1</v>
       </c>
-      <c r="AH7" s="43" t="s">
+      <c r="AH7" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="AI7" s="42">
+      <c r="AI7" s="39">
         <v>2</v>
       </c>
       <c r="AJ7" s="10">
         <v>2</v>
       </c>
       <c r="AK7" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL7" s="10">
         <v>0</v>
@@ -2869,35 +2869,35 @@
       <c r="AM7" s="14">
         <v>1</v>
       </c>
-      <c r="AN7" s="43" t="s">
+      <c r="AN7" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="AO7" s="42">
-        <v>2</v>
+      <c r="AO7" s="39">
+        <v>0</v>
       </c>
       <c r="AP7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ7" s="10">
         <v>0</v>
       </c>
       <c r="AR7" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS7" s="14">
         <v>0</v>
       </c>
-      <c r="AT7" s="44" t="s">
+      <c r="AT7" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU7" s="42">
+      <c r="AU7" s="39">
         <v>2</v>
       </c>
       <c r="AV7" s="10">
         <v>2</v>
       </c>
       <c r="AW7" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX7" s="10">
         <v>0</v>
@@ -2905,68 +2905,68 @@
       <c r="AY7" s="14">
         <v>1</v>
       </c>
-      <c r="AZ7" s="43" t="s">
+      <c r="AZ7" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="BA7" s="42">
-        <v>2</v>
+      <c r="BA7" s="39">
+        <v>0</v>
       </c>
       <c r="BB7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC7" s="10">
         <v>0</v>
       </c>
       <c r="BD7" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE7" s="14">
         <v>0</v>
       </c>
-      <c r="BF7" s="44" t="s">
+      <c r="BF7" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG7" s="45">
-        <v>2</v>
+      <c r="BG7" s="42">
+        <v>0</v>
       </c>
       <c r="BH7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI7" s="10">
         <v>0</v>
       </c>
       <c r="BJ7" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK7" s="14">
         <v>0</v>
       </c>
-      <c r="BL7" s="47" t="s">
+      <c r="BL7" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM7" s="30">
+      <c r="BM7" s="27">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="2:65" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:65" ht="45" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="3">
         <v>3</v>
       </c>
-      <c r="D8" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="42">
+      <c r="D8" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="39">
         <v>3</v>
       </c>
       <c r="F8" s="10">
         <v>3</v>
       </c>
       <c r="G8" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" s="10">
         <v>0</v>
@@ -2974,17 +2974,17 @@
       <c r="I8" s="14">
         <v>1</v>
       </c>
-      <c r="J8" s="43" t="s">
+      <c r="J8" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="42">
+      <c r="K8" s="39">
         <v>3</v>
       </c>
       <c r="L8" s="10">
         <v>3</v>
       </c>
       <c r="M8" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" s="10">
         <v>0</v>
@@ -2992,17 +2992,17 @@
       <c r="O8" s="14">
         <v>1</v>
       </c>
-      <c r="P8" s="43" t="s">
+      <c r="P8" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="Q8" s="42">
+      <c r="Q8" s="39">
         <v>3</v>
       </c>
       <c r="R8" s="10">
         <v>3</v>
       </c>
       <c r="S8" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T8" s="10">
         <v>0</v>
@@ -3010,17 +3010,17 @@
       <c r="U8" s="14">
         <v>1</v>
       </c>
-      <c r="V8" s="43" t="s">
+      <c r="V8" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="W8" s="42">
+      <c r="W8" s="39">
         <v>3</v>
       </c>
       <c r="X8" s="10">
         <v>3</v>
       </c>
       <c r="Y8" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="10">
         <v>0</v>
@@ -3028,17 +3028,17 @@
       <c r="AA8" s="14">
         <v>1</v>
       </c>
-      <c r="AB8" s="43" t="s">
+      <c r="AB8" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="AC8" s="42">
+      <c r="AC8" s="39">
         <v>3</v>
       </c>
       <c r="AD8" s="10">
         <v>3</v>
       </c>
       <c r="AE8" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="10">
         <v>0</v>
@@ -3046,17 +3046,17 @@
       <c r="AG8" s="14">
         <v>1</v>
       </c>
-      <c r="AH8" s="43" t="s">
+      <c r="AH8" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="AI8" s="42">
+      <c r="AI8" s="39">
         <v>3</v>
       </c>
       <c r="AJ8" s="10">
         <v>3</v>
       </c>
       <c r="AK8" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL8" s="10">
         <v>0</v>
@@ -3064,35 +3064,35 @@
       <c r="AM8" s="14">
         <v>1</v>
       </c>
-      <c r="AN8" s="43" t="s">
+      <c r="AN8" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="AO8" s="42">
-        <v>3</v>
+      <c r="AO8" s="39">
+        <v>1</v>
       </c>
       <c r="AP8" s="10">
         <v>1</v>
       </c>
       <c r="AQ8" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AS8" s="48">
+        <v>2</v>
+      </c>
+      <c r="AS8" s="45">
         <v>0.33333333333333298</v>
       </c>
-      <c r="AT8" s="44" t="s">
+      <c r="AT8" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="AU8" s="42">
+      <c r="AU8" s="39">
         <v>3</v>
       </c>
       <c r="AV8" s="10">
         <v>3</v>
       </c>
       <c r="AW8" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX8" s="10">
         <v>0</v>
@@ -3100,46 +3100,46 @@
       <c r="AY8" s="14">
         <v>1</v>
       </c>
-      <c r="AZ8" s="43" t="s">
+      <c r="AZ8" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="BA8" s="42">
-        <v>3</v>
+      <c r="BA8" s="39">
+        <v>1</v>
       </c>
       <c r="BB8" s="10">
         <v>1</v>
       </c>
       <c r="BC8" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD8" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE8" s="48">
+        <v>2</v>
+      </c>
+      <c r="BE8" s="45">
         <v>0.33333333333333298</v>
       </c>
-      <c r="BF8" s="44" t="s">
+      <c r="BF8" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="BG8" s="45">
-        <v>3</v>
+      <c r="BG8" s="42">
+        <v>0</v>
       </c>
       <c r="BH8" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI8" s="10">
         <v>0</v>
       </c>
       <c r="BJ8" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK8" s="14">
         <v>0</v>
       </c>
-      <c r="BL8" s="47" t="s">
+      <c r="BL8" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM8" s="30">
+      <c r="BM8" s="27">
         <f t="shared" si="0"/>
         <v>0.76666666666666661</v>
       </c>
@@ -3151,17 +3151,17 @@
       <c r="C9" s="3">
         <v>3</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="39">
         <v>3</v>
       </c>
       <c r="F9" s="10">
         <v>3</v>
       </c>
       <c r="G9" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H9" s="10">
         <v>0</v>
@@ -3169,17 +3169,17 @@
       <c r="I9" s="14">
         <v>1</v>
       </c>
-      <c r="J9" s="43" t="s">
+      <c r="J9" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K9" s="42">
+      <c r="K9" s="39">
         <v>3</v>
       </c>
       <c r="L9" s="10">
         <v>3</v>
       </c>
       <c r="M9" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" s="10">
         <v>0</v>
@@ -3187,17 +3187,17 @@
       <c r="O9" s="14">
         <v>1</v>
       </c>
-      <c r="P9" s="43" t="s">
+      <c r="P9" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="Q9" s="42">
+      <c r="Q9" s="39">
         <v>3</v>
       </c>
       <c r="R9" s="10">
         <v>3</v>
       </c>
       <c r="S9" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T9" s="10">
         <v>0</v>
@@ -3205,17 +3205,17 @@
       <c r="U9" s="14">
         <v>1</v>
       </c>
-      <c r="V9" s="43" t="s">
+      <c r="V9" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="W9" s="42">
+      <c r="W9" s="39">
         <v>3</v>
       </c>
       <c r="X9" s="10">
         <v>3</v>
       </c>
       <c r="Y9" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="10">
         <v>0</v>
@@ -3223,17 +3223,17 @@
       <c r="AA9" s="14">
         <v>1</v>
       </c>
-      <c r="AB9" s="43" t="s">
+      <c r="AB9" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="AC9" s="42">
+      <c r="AC9" s="39">
         <v>3</v>
       </c>
       <c r="AD9" s="10">
         <v>3</v>
       </c>
       <c r="AE9" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="10">
         <v>0</v>
@@ -3241,17 +3241,17 @@
       <c r="AG9" s="14">
         <v>1</v>
       </c>
-      <c r="AH9" s="43" t="s">
+      <c r="AH9" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="AI9" s="42">
+      <c r="AI9" s="39">
         <v>3</v>
       </c>
       <c r="AJ9" s="10">
         <v>3</v>
       </c>
       <c r="AK9" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL9" s="10">
         <v>0</v>
@@ -3259,35 +3259,35 @@
       <c r="AM9" s="14">
         <v>1</v>
       </c>
-      <c r="AN9" s="43" t="s">
+      <c r="AN9" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="AO9" s="42">
-        <v>3</v>
+      <c r="AO9" s="39">
+        <v>1</v>
       </c>
       <c r="AP9" s="10">
         <v>1</v>
       </c>
       <c r="AQ9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR9" s="10">
-        <v>0</v>
-      </c>
-      <c r="AS9" s="48">
+        <v>2</v>
+      </c>
+      <c r="AS9" s="45">
         <v>0.33333333333333298</v>
       </c>
-      <c r="AT9" s="44" t="s">
+      <c r="AT9" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="AU9" s="42">
+      <c r="AU9" s="39">
         <v>3</v>
       </c>
       <c r="AV9" s="10">
         <v>3</v>
       </c>
       <c r="AW9" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX9" s="10">
         <v>0</v>
@@ -3295,68 +3295,68 @@
       <c r="AY9" s="14">
         <v>1</v>
       </c>
-      <c r="AZ9" s="43" t="s">
+      <c r="AZ9" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="BA9" s="42">
-        <v>3</v>
+      <c r="BA9" s="39">
+        <v>1</v>
       </c>
       <c r="BB9" s="10">
         <v>1</v>
       </c>
       <c r="BC9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD9" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE9" s="48">
+        <v>2</v>
+      </c>
+      <c r="BE9" s="45">
         <v>0.33333333333333298</v>
       </c>
-      <c r="BF9" s="44" t="s">
+      <c r="BF9" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="BG9" s="45">
-        <v>3</v>
+      <c r="BG9" s="42">
+        <v>0</v>
       </c>
       <c r="BH9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI9" s="10">
         <v>0</v>
       </c>
       <c r="BJ9" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK9" s="14">
         <v>0</v>
       </c>
-      <c r="BL9" s="47" t="s">
+      <c r="BL9" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM9" s="30">
+      <c r="BM9" s="27">
         <f t="shared" si="0"/>
         <v>0.76666666666666661</v>
       </c>
     </row>
-    <row r="10" spans="2:65" ht="135" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:65" ht="90" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="3">
         <v>6</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="39">
         <v>6</v>
       </c>
       <c r="F10" s="10">
         <v>6</v>
       </c>
       <c r="G10" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H10" s="10">
         <v>0</v>
@@ -3364,17 +3364,17 @@
       <c r="I10" s="14">
         <v>1</v>
       </c>
-      <c r="J10" s="43" t="s">
+      <c r="J10" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="42">
+      <c r="K10" s="39">
         <v>6</v>
       </c>
       <c r="L10" s="10">
         <v>6</v>
       </c>
       <c r="M10" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N10" s="10">
         <v>0</v>
@@ -3382,17 +3382,17 @@
       <c r="O10" s="14">
         <v>1</v>
       </c>
-      <c r="P10" s="43" t="s">
+      <c r="P10" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="Q10" s="42">
+      <c r="Q10" s="39">
         <v>6</v>
       </c>
       <c r="R10" s="10">
         <v>6</v>
       </c>
       <c r="S10" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T10" s="10">
         <v>0</v>
@@ -3400,17 +3400,17 @@
       <c r="U10" s="14">
         <v>1</v>
       </c>
-      <c r="V10" s="43" t="s">
+      <c r="V10" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="W10" s="42">
+      <c r="W10" s="39">
         <v>6</v>
       </c>
       <c r="X10" s="10">
         <v>6</v>
       </c>
       <c r="Y10" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="10">
         <v>0</v>
@@ -3418,17 +3418,17 @@
       <c r="AA10" s="14">
         <v>1</v>
       </c>
-      <c r="AB10" s="43" t="s">
+      <c r="AB10" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="AC10" s="42">
+      <c r="AC10" s="39">
         <v>6</v>
       </c>
       <c r="AD10" s="10">
         <v>6</v>
       </c>
       <c r="AE10" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="10">
         <v>0</v>
@@ -3436,17 +3436,17 @@
       <c r="AG10" s="14">
         <v>1</v>
       </c>
-      <c r="AH10" s="43" t="s">
+      <c r="AH10" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="AI10" s="42">
+      <c r="AI10" s="39">
         <v>6</v>
       </c>
       <c r="AJ10" s="10">
         <v>6</v>
       </c>
       <c r="AK10" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AL10" s="10">
         <v>0</v>
@@ -3454,35 +3454,35 @@
       <c r="AM10" s="14">
         <v>1</v>
       </c>
-      <c r="AN10" s="43" t="s">
+      <c r="AN10" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="AO10" s="42">
-        <v>6</v>
+      <c r="AO10" s="39">
+        <v>0</v>
       </c>
       <c r="AP10" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ10" s="10">
         <v>0</v>
       </c>
       <c r="AR10" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AS10" s="14">
         <v>0</v>
       </c>
-      <c r="AT10" s="44" t="s">
+      <c r="AT10" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU10" s="42">
+      <c r="AU10" s="39">
         <v>6</v>
       </c>
       <c r="AV10" s="10">
         <v>6</v>
       </c>
       <c r="AW10" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AX10" s="10">
         <v>0</v>
@@ -3490,68 +3490,68 @@
       <c r="AY10" s="14">
         <v>1</v>
       </c>
-      <c r="AZ10" s="43" t="s">
+      <c r="AZ10" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="BA10" s="42">
-        <v>6</v>
+      <c r="BA10" s="39">
+        <v>0</v>
       </c>
       <c r="BB10" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC10" s="10">
         <v>0</v>
       </c>
       <c r="BD10" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BE10" s="14">
         <v>0</v>
       </c>
-      <c r="BF10" s="44" t="s">
+      <c r="BF10" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG10" s="45">
-        <v>6</v>
+      <c r="BG10" s="42">
+        <v>0</v>
       </c>
       <c r="BH10" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI10" s="10">
         <v>0</v>
       </c>
       <c r="BJ10" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BK10" s="14">
         <v>0</v>
       </c>
-      <c r="BL10" s="47" t="s">
+      <c r="BL10" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM10" s="30">
+      <c r="BM10" s="27">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="2:65" ht="195" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:65" ht="90" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="3">
         <v>6</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="39">
         <v>6</v>
       </c>
       <c r="F11" s="10">
         <v>6</v>
       </c>
       <c r="G11" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H11" s="10">
         <v>0</v>
@@ -3559,17 +3559,17 @@
       <c r="I11" s="14">
         <v>1</v>
       </c>
-      <c r="J11" s="43" t="s">
+      <c r="J11" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="42">
+      <c r="K11" s="39">
         <v>6</v>
       </c>
       <c r="L11" s="10">
         <v>6</v>
       </c>
       <c r="M11" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N11" s="10">
         <v>0</v>
@@ -3577,17 +3577,17 @@
       <c r="O11" s="14">
         <v>1</v>
       </c>
-      <c r="P11" s="43" t="s">
+      <c r="P11" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="Q11" s="42">
+      <c r="Q11" s="39">
         <v>6</v>
       </c>
       <c r="R11" s="10">
         <v>6</v>
       </c>
       <c r="S11" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T11" s="10">
         <v>0</v>
@@ -3595,17 +3595,17 @@
       <c r="U11" s="14">
         <v>1</v>
       </c>
-      <c r="V11" s="43" t="s">
+      <c r="V11" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="W11" s="42">
+      <c r="W11" s="39">
         <v>6</v>
       </c>
       <c r="X11" s="10">
         <v>6</v>
       </c>
       <c r="Y11" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="10">
         <v>0</v>
@@ -3613,17 +3613,17 @@
       <c r="AA11" s="14">
         <v>1</v>
       </c>
-      <c r="AB11" s="43" t="s">
+      <c r="AB11" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="AC11" s="42">
+      <c r="AC11" s="39">
         <v>6</v>
       </c>
       <c r="AD11" s="10">
         <v>6</v>
       </c>
       <c r="AE11" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF11" s="10">
         <v>0</v>
@@ -3631,17 +3631,17 @@
       <c r="AG11" s="14">
         <v>1</v>
       </c>
-      <c r="AH11" s="43" t="s">
+      <c r="AH11" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="AI11" s="42">
+      <c r="AI11" s="39">
         <v>6</v>
       </c>
       <c r="AJ11" s="10">
         <v>6</v>
       </c>
       <c r="AK11" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AL11" s="10">
         <v>0</v>
@@ -3649,35 +3649,35 @@
       <c r="AM11" s="14">
         <v>1</v>
       </c>
-      <c r="AN11" s="43" t="s">
+      <c r="AN11" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="AO11" s="42">
-        <v>6</v>
+      <c r="AO11" s="39">
+        <v>0</v>
       </c>
       <c r="AP11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ11" s="10">
         <v>0</v>
       </c>
       <c r="AR11" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AS11" s="14">
         <v>0</v>
       </c>
-      <c r="AT11" s="44" t="s">
+      <c r="AT11" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU11" s="42">
+      <c r="AU11" s="39">
         <v>6</v>
       </c>
       <c r="AV11" s="10">
         <v>6</v>
       </c>
       <c r="AW11" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AX11" s="10">
         <v>0</v>
@@ -3685,46 +3685,46 @@
       <c r="AY11" s="14">
         <v>1</v>
       </c>
-      <c r="AZ11" s="43" t="s">
+      <c r="AZ11" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="BA11" s="42">
-        <v>6</v>
+      <c r="BA11" s="39">
+        <v>0</v>
       </c>
       <c r="BB11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC11" s="10">
         <v>0</v>
       </c>
       <c r="BD11" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BE11" s="14">
         <v>0</v>
       </c>
-      <c r="BF11" s="44" t="s">
+      <c r="BF11" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG11" s="45">
-        <v>6</v>
+      <c r="BG11" s="42">
+        <v>0</v>
       </c>
       <c r="BH11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI11" s="10">
         <v>0</v>
       </c>
       <c r="BJ11" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BK11" s="14">
         <v>0</v>
       </c>
-      <c r="BL11" s="47" t="s">
+      <c r="BL11" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM11" s="30">
+      <c r="BM11" s="27">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
@@ -3736,14 +3736,14 @@
       <c r="C12" s="3">
         <v>1</v>
       </c>
-      <c r="D12" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="E12" s="42">
-        <v>1</v>
+      <c r="D12" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="39">
+        <v>0</v>
       </c>
       <c r="F12" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="10">
         <v>0</v>
@@ -3754,12 +3754,12 @@
       <c r="I12" s="14">
         <v>0</v>
       </c>
-      <c r="J12" s="44"/>
-      <c r="K12" s="42">
-        <v>1</v>
+      <c r="J12" s="41"/>
+      <c r="K12" s="39">
+        <v>0</v>
       </c>
       <c r="L12" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="10">
         <v>0</v>
@@ -3770,12 +3770,12 @@
       <c r="O12" s="14">
         <v>0</v>
       </c>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="42">
-        <v>1</v>
+      <c r="P12" s="41"/>
+      <c r="Q12" s="39">
+        <v>0</v>
       </c>
       <c r="R12" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="10">
         <v>0</v>
@@ -3786,12 +3786,12 @@
       <c r="U12" s="14">
         <v>0</v>
       </c>
-      <c r="V12" s="44"/>
-      <c r="W12" s="42">
-        <v>1</v>
+      <c r="V12" s="41"/>
+      <c r="W12" s="39">
+        <v>0</v>
       </c>
       <c r="X12" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="10">
         <v>0</v>
@@ -3802,12 +3802,12 @@
       <c r="AA12" s="14">
         <v>0</v>
       </c>
-      <c r="AB12" s="44"/>
-      <c r="AC12" s="42">
-        <v>1</v>
+      <c r="AB12" s="41"/>
+      <c r="AC12" s="39">
+        <v>0</v>
       </c>
       <c r="AD12" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="10">
         <v>0</v>
@@ -3818,12 +3818,12 @@
       <c r="AG12" s="14">
         <v>0</v>
       </c>
-      <c r="AH12" s="44"/>
-      <c r="AI12" s="42">
-        <v>1</v>
+      <c r="AH12" s="41"/>
+      <c r="AI12" s="39">
+        <v>0</v>
       </c>
       <c r="AJ12" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="10">
         <v>0</v>
@@ -3834,12 +3834,12 @@
       <c r="AM12" s="14">
         <v>0</v>
       </c>
-      <c r="AN12" s="44"/>
-      <c r="AO12" s="42">
-        <v>1</v>
+      <c r="AN12" s="41"/>
+      <c r="AO12" s="39">
+        <v>0</v>
       </c>
       <c r="AP12" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ12" s="10">
         <v>0</v>
@@ -3850,14 +3850,14 @@
       <c r="AS12" s="14">
         <v>0</v>
       </c>
-      <c r="AT12" s="44" t="s">
+      <c r="AT12" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU12" s="42">
-        <v>1</v>
+      <c r="AU12" s="39">
+        <v>0</v>
       </c>
       <c r="AV12" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW12" s="10">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       <c r="AY12" s="14">
         <v>0</v>
       </c>
-      <c r="AZ12" s="44"/>
-      <c r="BA12" s="42">
-        <v>1</v>
+      <c r="AZ12" s="41"/>
+      <c r="BA12" s="39">
+        <v>0</v>
       </c>
       <c r="BB12" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC12" s="10">
         <v>0</v>
@@ -3884,14 +3884,14 @@
       <c r="BE12" s="14">
         <v>0</v>
       </c>
-      <c r="BF12" s="44" t="s">
+      <c r="BF12" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG12" s="45">
-        <v>1</v>
+      <c r="BG12" s="42">
+        <v>0</v>
       </c>
       <c r="BH12" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI12" s="10">
         <v>0</v>
@@ -3902,10 +3902,10 @@
       <c r="BK12" s="14">
         <v>0</v>
       </c>
-      <c r="BL12" s="47" t="s">
+      <c r="BL12" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM12" s="30">
+      <c r="BM12" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3917,17 +3917,17 @@
       <c r="C13" s="3">
         <v>1</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="39">
         <v>1</v>
       </c>
       <c r="F13" s="10">
         <v>1</v>
       </c>
       <c r="G13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="10">
         <v>0</v>
@@ -3935,17 +3935,17 @@
       <c r="I13" s="14">
         <v>1</v>
       </c>
-      <c r="J13" s="44" t="s">
+      <c r="J13" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="42">
+      <c r="K13" s="39">
         <v>1</v>
       </c>
       <c r="L13" s="10">
         <v>1</v>
       </c>
       <c r="M13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="10">
         <v>0</v>
@@ -3953,17 +3953,17 @@
       <c r="O13" s="14">
         <v>1</v>
       </c>
-      <c r="P13" s="44" t="s">
+      <c r="P13" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="Q13" s="42">
+      <c r="Q13" s="39">
         <v>1</v>
       </c>
       <c r="R13" s="10">
         <v>1</v>
       </c>
       <c r="S13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" s="10">
         <v>0</v>
@@ -3971,17 +3971,17 @@
       <c r="U13" s="14">
         <v>1</v>
       </c>
-      <c r="V13" s="44" t="s">
+      <c r="V13" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="W13" s="42">
+      <c r="W13" s="39">
         <v>1</v>
       </c>
       <c r="X13" s="10">
         <v>1</v>
       </c>
       <c r="Y13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="10">
         <v>0</v>
@@ -3989,17 +3989,17 @@
       <c r="AA13" s="14">
         <v>1</v>
       </c>
-      <c r="AB13" s="44" t="s">
+      <c r="AB13" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="AC13" s="42">
+      <c r="AC13" s="39">
         <v>1</v>
       </c>
       <c r="AD13" s="10">
         <v>1</v>
       </c>
       <c r="AE13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF13" s="10">
         <v>0</v>
@@ -4007,17 +4007,17 @@
       <c r="AG13" s="14">
         <v>1</v>
       </c>
-      <c r="AH13" s="44" t="s">
+      <c r="AH13" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="AI13" s="42">
+      <c r="AI13" s="39">
         <v>1</v>
       </c>
       <c r="AJ13" s="10">
         <v>1</v>
       </c>
       <c r="AK13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL13" s="10">
         <v>0</v>
@@ -4025,14 +4025,14 @@
       <c r="AM13" s="14">
         <v>1</v>
       </c>
-      <c r="AN13" s="44" t="s">
+      <c r="AN13" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="AO13" s="42">
-        <v>1</v>
+      <c r="AO13" s="39">
+        <v>0</v>
       </c>
       <c r="AP13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ13" s="10">
         <v>0</v>
@@ -4043,17 +4043,17 @@
       <c r="AS13" s="14">
         <v>0</v>
       </c>
-      <c r="AT13" s="44" t="s">
+      <c r="AT13" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU13" s="42">
+      <c r="AU13" s="39">
         <v>1</v>
       </c>
       <c r="AV13" s="10">
         <v>1</v>
       </c>
       <c r="AW13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX13" s="10">
         <v>0</v>
@@ -4061,14 +4061,14 @@
       <c r="AY13" s="14">
         <v>1</v>
       </c>
-      <c r="AZ13" s="44" t="s">
+      <c r="AZ13" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="BA13" s="42">
-        <v>1</v>
+      <c r="BA13" s="39">
+        <v>0</v>
       </c>
       <c r="BB13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC13" s="10">
         <v>0</v>
@@ -4079,14 +4079,14 @@
       <c r="BE13" s="14">
         <v>0</v>
       </c>
-      <c r="BF13" s="44" t="s">
+      <c r="BF13" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG13" s="45">
-        <v>1</v>
+      <c r="BG13" s="42">
+        <v>0</v>
       </c>
       <c r="BH13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI13" s="10">
         <v>0</v>
@@ -4097,10 +4097,10 @@
       <c r="BK13" s="14">
         <v>0</v>
       </c>
-      <c r="BL13" s="47" t="s">
+      <c r="BL13" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM13" s="30">
+      <c r="BM13" s="27">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
@@ -4112,17 +4112,17 @@
       <c r="C14" s="3">
         <v>3</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="39">
         <v>3</v>
       </c>
       <c r="F14" s="10">
         <v>3</v>
       </c>
       <c r="G14" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H14" s="10">
         <v>0</v>
@@ -4130,17 +4130,17 @@
       <c r="I14" s="14">
         <v>1</v>
       </c>
-      <c r="J14" s="43" t="s">
+      <c r="J14" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="K14" s="42">
+      <c r="K14" s="39">
         <v>3</v>
       </c>
       <c r="L14" s="10">
         <v>3</v>
       </c>
       <c r="M14" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N14" s="10">
         <v>0</v>
@@ -4148,17 +4148,17 @@
       <c r="O14" s="14">
         <v>1</v>
       </c>
-      <c r="P14" s="43" t="s">
+      <c r="P14" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="Q14" s="42">
+      <c r="Q14" s="39">
         <v>3</v>
       </c>
       <c r="R14" s="10">
         <v>3</v>
       </c>
       <c r="S14" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T14" s="10">
         <v>0</v>
@@ -4166,17 +4166,17 @@
       <c r="U14" s="14">
         <v>1</v>
       </c>
-      <c r="V14" s="43" t="s">
+      <c r="V14" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="W14" s="42">
+      <c r="W14" s="39">
         <v>3</v>
       </c>
       <c r="X14" s="10">
         <v>3</v>
       </c>
       <c r="Y14" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="10">
         <v>0</v>
@@ -4184,17 +4184,17 @@
       <c r="AA14" s="14">
         <v>1</v>
       </c>
-      <c r="AB14" s="43" t="s">
+      <c r="AB14" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="AC14" s="42">
+      <c r="AC14" s="39">
         <v>3</v>
       </c>
       <c r="AD14" s="10">
         <v>3</v>
       </c>
       <c r="AE14" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF14" s="10">
         <v>0</v>
@@ -4202,17 +4202,17 @@
       <c r="AG14" s="14">
         <v>1</v>
       </c>
-      <c r="AH14" s="43" t="s">
+      <c r="AH14" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="AI14" s="42">
+      <c r="AI14" s="39">
         <v>3</v>
       </c>
       <c r="AJ14" s="10">
         <v>3</v>
       </c>
       <c r="AK14" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL14" s="10">
         <v>0</v>
@@ -4220,35 +4220,35 @@
       <c r="AM14" s="14">
         <v>1</v>
       </c>
-      <c r="AN14" s="43" t="s">
+      <c r="AN14" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="42">
-        <v>3</v>
+      <c r="AO14" s="39">
+        <v>0</v>
       </c>
       <c r="AP14" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ14" s="10">
         <v>0</v>
       </c>
       <c r="AR14" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS14" s="14">
         <v>0</v>
       </c>
-      <c r="AT14" s="44" t="s">
+      <c r="AT14" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU14" s="42">
+      <c r="AU14" s="39">
         <v>3</v>
       </c>
       <c r="AV14" s="10">
         <v>3</v>
       </c>
       <c r="AW14" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX14" s="10">
         <v>0</v>
@@ -4256,68 +4256,68 @@
       <c r="AY14" s="14">
         <v>1</v>
       </c>
-      <c r="AZ14" s="43" t="s">
+      <c r="AZ14" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="BA14" s="42">
-        <v>3</v>
+      <c r="BA14" s="39">
+        <v>0</v>
       </c>
       <c r="BB14" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC14" s="10">
         <v>0</v>
       </c>
       <c r="BD14" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BE14" s="14">
         <v>0</v>
       </c>
-      <c r="BF14" s="44" t="s">
+      <c r="BF14" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG14" s="45">
-        <v>3</v>
+      <c r="BG14" s="42">
+        <v>0</v>
       </c>
       <c r="BH14" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI14" s="10">
         <v>0</v>
       </c>
       <c r="BJ14" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK14" s="14">
         <v>0</v>
       </c>
-      <c r="BL14" s="47" t="s">
+      <c r="BL14" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM14" s="30">
+      <c r="BM14" s="27">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="15" spans="2:65" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:65" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C15" s="3">
         <v>2</v>
       </c>
-      <c r="D15" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="42">
+      <c r="D15" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="39">
         <v>2</v>
       </c>
       <c r="F15" s="10">
         <v>2</v>
       </c>
       <c r="G15" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" s="10">
         <v>0</v>
@@ -4325,17 +4325,17 @@
       <c r="I15" s="14">
         <v>1</v>
       </c>
-      <c r="J15" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="K15" s="42">
+      <c r="J15" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="K15" s="39">
         <v>2</v>
       </c>
       <c r="L15" s="10">
         <v>2</v>
       </c>
       <c r="M15" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N15" s="10">
         <v>0</v>
@@ -4343,17 +4343,17 @@
       <c r="O15" s="14">
         <v>1</v>
       </c>
-      <c r="P15" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="42">
+      <c r="P15" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="39">
         <v>2</v>
       </c>
       <c r="R15" s="10">
         <v>2</v>
       </c>
       <c r="S15" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T15" s="10">
         <v>0</v>
@@ -4361,17 +4361,17 @@
       <c r="U15" s="14">
         <v>1</v>
       </c>
-      <c r="V15" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="W15" s="42">
+      <c r="V15" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="W15" s="39">
         <v>2</v>
       </c>
       <c r="X15" s="10">
         <v>2</v>
       </c>
       <c r="Y15" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="10">
         <v>0</v>
@@ -4379,17 +4379,17 @@
       <c r="AA15" s="14">
         <v>1</v>
       </c>
-      <c r="AB15" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC15" s="42">
+      <c r="AB15" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC15" s="39">
         <v>2</v>
       </c>
       <c r="AD15" s="10">
         <v>2</v>
       </c>
       <c r="AE15" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF15" s="10">
         <v>0</v>
@@ -4397,17 +4397,17 @@
       <c r="AG15" s="14">
         <v>1</v>
       </c>
-      <c r="AH15" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI15" s="42">
+      <c r="AH15" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI15" s="39">
         <v>2</v>
       </c>
       <c r="AJ15" s="10">
         <v>2</v>
       </c>
       <c r="AK15" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL15" s="10">
         <v>0</v>
@@ -4415,35 +4415,35 @@
       <c r="AM15" s="14">
         <v>1</v>
       </c>
-      <c r="AN15" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO15" s="42">
-        <v>2</v>
+      <c r="AN15" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO15" s="39">
+        <v>0</v>
       </c>
       <c r="AP15" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ15" s="10">
         <v>0</v>
       </c>
       <c r="AR15" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS15" s="14">
         <v>0</v>
       </c>
-      <c r="AT15" s="44" t="s">
+      <c r="AT15" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU15" s="42">
+      <c r="AU15" s="39">
         <v>2</v>
       </c>
       <c r="AV15" s="10">
         <v>2</v>
       </c>
       <c r="AW15" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX15" s="10">
         <v>0</v>
@@ -4451,35 +4451,35 @@
       <c r="AY15" s="14">
         <v>1</v>
       </c>
-      <c r="AZ15" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="BA15" s="42">
-        <v>2</v>
+      <c r="AZ15" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="BA15" s="39">
+        <v>0</v>
       </c>
       <c r="BB15" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC15" s="10">
         <v>0</v>
       </c>
       <c r="BD15" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE15" s="14">
         <v>0</v>
       </c>
-      <c r="BF15" s="44" t="s">
+      <c r="BF15" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG15" s="45">
+      <c r="BG15" s="42">
         <v>2</v>
       </c>
       <c r="BH15" s="10">
         <v>2</v>
       </c>
       <c r="BI15" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ15" s="10">
         <v>0</v>
@@ -4487,32 +4487,32 @@
       <c r="BK15" s="14">
         <v>1</v>
       </c>
-      <c r="BL15" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="BM15" s="30">
+      <c r="BL15" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="BM15" s="27">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:65" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:65" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C16" s="3">
         <v>2</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="39">
         <v>2</v>
       </c>
       <c r="F16" s="10">
         <v>2</v>
       </c>
       <c r="G16" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16" s="10">
         <v>0</v>
@@ -4520,17 +4520,17 @@
       <c r="I16" s="14">
         <v>1</v>
       </c>
-      <c r="J16" s="43" t="s">
+      <c r="J16" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="K16" s="42">
+      <c r="K16" s="39">
         <v>2</v>
       </c>
       <c r="L16" s="10">
         <v>2</v>
       </c>
       <c r="M16" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16" s="10">
         <v>0</v>
@@ -4538,17 +4538,17 @@
       <c r="O16" s="14">
         <v>1</v>
       </c>
-      <c r="P16" s="43" t="s">
+      <c r="P16" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="Q16" s="42">
+      <c r="Q16" s="39">
         <v>2</v>
       </c>
       <c r="R16" s="10">
         <v>2</v>
       </c>
       <c r="S16" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T16" s="10">
         <v>0</v>
@@ -4556,17 +4556,17 @@
       <c r="U16" s="14">
         <v>1</v>
       </c>
-      <c r="V16" s="43" t="s">
+      <c r="V16" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="W16" s="42">
+      <c r="W16" s="39">
         <v>2</v>
       </c>
       <c r="X16" s="10">
         <v>2</v>
       </c>
       <c r="Y16" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="10">
         <v>0</v>
@@ -4574,17 +4574,17 @@
       <c r="AA16" s="14">
         <v>1</v>
       </c>
-      <c r="AB16" s="43" t="s">
+      <c r="AB16" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="AC16" s="42">
+      <c r="AC16" s="39">
         <v>2</v>
       </c>
       <c r="AD16" s="10">
         <v>2</v>
       </c>
       <c r="AE16" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF16" s="10">
         <v>0</v>
@@ -4592,17 +4592,17 @@
       <c r="AG16" s="14">
         <v>1</v>
       </c>
-      <c r="AH16" s="43" t="s">
+      <c r="AH16" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="AI16" s="42">
+      <c r="AI16" s="39">
         <v>2</v>
       </c>
       <c r="AJ16" s="10">
         <v>2</v>
       </c>
       <c r="AK16" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL16" s="10">
         <v>0</v>
@@ -4610,35 +4610,35 @@
       <c r="AM16" s="14">
         <v>1</v>
       </c>
-      <c r="AN16" s="43" t="s">
+      <c r="AN16" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="AO16" s="42">
-        <v>2</v>
+      <c r="AO16" s="39">
+        <v>0</v>
       </c>
       <c r="AP16" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ16" s="10">
         <v>0</v>
       </c>
       <c r="AR16" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS16" s="14">
         <v>0</v>
       </c>
-      <c r="AT16" s="44" t="s">
+      <c r="AT16" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU16" s="42">
+      <c r="AU16" s="39">
         <v>2</v>
       </c>
       <c r="AV16" s="10">
         <v>2</v>
       </c>
       <c r="AW16" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX16" s="10">
         <v>0</v>
@@ -4646,35 +4646,35 @@
       <c r="AY16" s="14">
         <v>1</v>
       </c>
-      <c r="AZ16" s="43" t="s">
+      <c r="AZ16" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="BA16" s="42">
-        <v>2</v>
+      <c r="BA16" s="39">
+        <v>0</v>
       </c>
       <c r="BB16" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC16" s="10">
         <v>0</v>
       </c>
       <c r="BD16" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE16" s="14">
         <v>0</v>
       </c>
-      <c r="BF16" s="44" t="s">
+      <c r="BF16" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG16" s="45">
+      <c r="BG16" s="42">
         <v>2</v>
       </c>
       <c r="BH16" s="10">
         <v>2</v>
       </c>
       <c r="BI16" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ16" s="10">
         <v>0</v>
@@ -4682,10 +4682,10 @@
       <c r="BK16" s="14">
         <v>1</v>
       </c>
-      <c r="BL16" s="46" t="s">
+      <c r="BL16" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="BM16" s="30">
+      <c r="BM16" s="27">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
@@ -4697,17 +4697,17 @@
       <c r="C17" s="3">
         <v>2</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="39">
         <v>2</v>
       </c>
       <c r="F17" s="10">
         <v>2</v>
       </c>
       <c r="G17" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" s="10">
         <v>0</v>
@@ -4715,17 +4715,17 @@
       <c r="I17" s="14">
         <v>1</v>
       </c>
-      <c r="J17" s="43" t="s">
+      <c r="J17" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="42">
+      <c r="K17" s="39">
         <v>2</v>
       </c>
       <c r="L17" s="10">
         <v>2</v>
       </c>
       <c r="M17" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N17" s="10">
         <v>0</v>
@@ -4733,17 +4733,17 @@
       <c r="O17" s="14">
         <v>1</v>
       </c>
-      <c r="P17" s="43" t="s">
+      <c r="P17" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="Q17" s="42">
+      <c r="Q17" s="39">
         <v>2</v>
       </c>
       <c r="R17" s="10">
         <v>2</v>
       </c>
       <c r="S17" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
@@ -4751,17 +4751,17 @@
       <c r="U17" s="14">
         <v>1</v>
       </c>
-      <c r="V17" s="43" t="s">
+      <c r="V17" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="W17" s="42">
+      <c r="W17" s="39">
         <v>2</v>
       </c>
       <c r="X17" s="10">
         <v>2</v>
       </c>
       <c r="Y17" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="10">
         <v>0</v>
@@ -4769,17 +4769,17 @@
       <c r="AA17" s="14">
         <v>1</v>
       </c>
-      <c r="AB17" s="43" t="s">
+      <c r="AB17" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="AC17" s="42">
+      <c r="AC17" s="39">
         <v>2</v>
       </c>
       <c r="AD17" s="10">
         <v>2</v>
       </c>
       <c r="AE17" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF17" s="10">
         <v>0</v>
@@ -4787,17 +4787,17 @@
       <c r="AG17" s="14">
         <v>1</v>
       </c>
-      <c r="AH17" s="43" t="s">
+      <c r="AH17" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="AI17" s="42">
+      <c r="AI17" s="39">
         <v>2</v>
       </c>
       <c r="AJ17" s="10">
         <v>2</v>
       </c>
       <c r="AK17" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL17" s="10">
         <v>0</v>
@@ -4805,35 +4805,35 @@
       <c r="AM17" s="14">
         <v>1</v>
       </c>
-      <c r="AN17" s="43" t="s">
+      <c r="AN17" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="AO17" s="42">
-        <v>2</v>
+      <c r="AO17" s="39">
+        <v>0</v>
       </c>
       <c r="AP17" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ17" s="10">
         <v>0</v>
       </c>
       <c r="AR17" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS17" s="14">
         <v>0</v>
       </c>
-      <c r="AT17" s="44" t="s">
+      <c r="AT17" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU17" s="42">
+      <c r="AU17" s="39">
         <v>2</v>
       </c>
       <c r="AV17" s="10">
         <v>2</v>
       </c>
       <c r="AW17" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX17" s="10">
         <v>0</v>
@@ -4841,68 +4841,68 @@
       <c r="AY17" s="14">
         <v>1</v>
       </c>
-      <c r="AZ17" s="43" t="s">
+      <c r="AZ17" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="BA17" s="42">
-        <v>2</v>
+      <c r="BA17" s="39">
+        <v>0</v>
       </c>
       <c r="BB17" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC17" s="10">
         <v>0</v>
       </c>
       <c r="BD17" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE17" s="14">
         <v>0</v>
       </c>
-      <c r="BF17" s="44" t="s">
+      <c r="BF17" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG17" s="45">
-        <v>2</v>
+      <c r="BG17" s="42">
+        <v>0</v>
       </c>
       <c r="BH17" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI17" s="10">
         <v>0</v>
       </c>
       <c r="BJ17" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK17" s="14">
         <v>0</v>
       </c>
-      <c r="BL17" s="47" t="s">
+      <c r="BL17" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM17" s="30">
+      <c r="BM17" s="27">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="18" spans="2:65" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:65" ht="45" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C18" s="3">
         <v>3</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="42">
+      <c r="E18" s="39">
         <v>3</v>
       </c>
       <c r="F18" s="10">
         <v>3</v>
       </c>
       <c r="G18" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" s="10">
         <v>0</v>
@@ -4910,17 +4910,17 @@
       <c r="I18" s="14">
         <v>1</v>
       </c>
-      <c r="J18" s="43" t="s">
+      <c r="J18" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="K18" s="42">
+      <c r="K18" s="39">
         <v>3</v>
       </c>
       <c r="L18" s="10">
         <v>3</v>
       </c>
       <c r="M18" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" s="10">
         <v>0</v>
@@ -4928,17 +4928,17 @@
       <c r="O18" s="14">
         <v>1</v>
       </c>
-      <c r="P18" s="43" t="s">
+      <c r="P18" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="Q18" s="42">
+      <c r="Q18" s="39">
         <v>3</v>
       </c>
       <c r="R18" s="10">
         <v>3</v>
       </c>
       <c r="S18" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T18" s="10">
         <v>0</v>
@@ -4946,17 +4946,17 @@
       <c r="U18" s="14">
         <v>1</v>
       </c>
-      <c r="V18" s="43" t="s">
+      <c r="V18" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="W18" s="42">
+      <c r="W18" s="39">
         <v>3</v>
       </c>
       <c r="X18" s="10">
         <v>3</v>
       </c>
       <c r="Y18" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="10">
         <v>0</v>
@@ -4964,17 +4964,17 @@
       <c r="AA18" s="14">
         <v>1</v>
       </c>
-      <c r="AB18" s="43" t="s">
+      <c r="AB18" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="AC18" s="42">
+      <c r="AC18" s="39">
         <v>3</v>
       </c>
       <c r="AD18" s="10">
         <v>3</v>
       </c>
       <c r="AE18" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF18" s="10">
         <v>0</v>
@@ -4982,17 +4982,17 @@
       <c r="AG18" s="14">
         <v>1</v>
       </c>
-      <c r="AH18" s="43" t="s">
+      <c r="AH18" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="AI18" s="42">
+      <c r="AI18" s="39">
         <v>3</v>
       </c>
       <c r="AJ18" s="10">
         <v>3</v>
       </c>
       <c r="AK18" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL18" s="10">
         <v>0</v>
@@ -5000,35 +5000,35 @@
       <c r="AM18" s="14">
         <v>1</v>
       </c>
-      <c r="AN18" s="43" t="s">
+      <c r="AN18" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="AO18" s="42">
-        <v>3</v>
+      <c r="AO18" s="39">
+        <v>0</v>
       </c>
       <c r="AP18" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ18" s="10">
         <v>0</v>
       </c>
       <c r="AR18" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS18" s="14">
         <v>0</v>
       </c>
-      <c r="AT18" s="44" t="s">
+      <c r="AT18" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU18" s="42">
+      <c r="AU18" s="39">
         <v>3</v>
       </c>
       <c r="AV18" s="10">
         <v>3</v>
       </c>
       <c r="AW18" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX18" s="10">
         <v>0</v>
@@ -5036,46 +5036,46 @@
       <c r="AY18" s="14">
         <v>1</v>
       </c>
-      <c r="AZ18" s="43" t="s">
+      <c r="AZ18" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="BA18" s="42">
-        <v>3</v>
+      <c r="BA18" s="39">
+        <v>0</v>
       </c>
       <c r="BB18" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC18" s="10">
         <v>0</v>
       </c>
       <c r="BD18" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BE18" s="14">
         <v>0</v>
       </c>
-      <c r="BF18" s="44" t="s">
+      <c r="BF18" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG18" s="45">
-        <v>3</v>
+      <c r="BG18" s="42">
+        <v>0</v>
       </c>
       <c r="BH18" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI18" s="10">
         <v>0</v>
       </c>
       <c r="BJ18" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK18" s="14">
         <v>0</v>
       </c>
-      <c r="BL18" s="47" t="s">
+      <c r="BL18" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM18" s="30">
+      <c r="BM18" s="27">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
@@ -5087,17 +5087,17 @@
       <c r="C19" s="3">
         <v>3</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="42">
+      <c r="E19" s="39">
         <v>3</v>
       </c>
       <c r="F19" s="10">
         <v>3</v>
       </c>
       <c r="G19" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H19" s="10">
         <v>0</v>
@@ -5105,17 +5105,17 @@
       <c r="I19" s="14">
         <v>1</v>
       </c>
-      <c r="J19" s="43" t="s">
+      <c r="J19" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="K19" s="42">
+      <c r="K19" s="39">
         <v>3</v>
       </c>
       <c r="L19" s="10">
         <v>3</v>
       </c>
       <c r="M19" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" s="10">
         <v>0</v>
@@ -5123,17 +5123,17 @@
       <c r="O19" s="14">
         <v>1</v>
       </c>
-      <c r="P19" s="43" t="s">
+      <c r="P19" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="Q19" s="42">
+      <c r="Q19" s="39">
         <v>3</v>
       </c>
       <c r="R19" s="10">
         <v>3</v>
       </c>
       <c r="S19" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
@@ -5141,17 +5141,17 @@
       <c r="U19" s="14">
         <v>1</v>
       </c>
-      <c r="V19" s="43" t="s">
+      <c r="V19" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="W19" s="42">
+      <c r="W19" s="39">
         <v>3</v>
       </c>
       <c r="X19" s="10">
         <v>3</v>
       </c>
       <c r="Y19" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="10">
         <v>0</v>
@@ -5159,17 +5159,17 @@
       <c r="AA19" s="14">
         <v>1</v>
       </c>
-      <c r="AB19" s="43" t="s">
+      <c r="AB19" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="AC19" s="42">
+      <c r="AC19" s="39">
         <v>3</v>
       </c>
       <c r="AD19" s="10">
         <v>3</v>
       </c>
       <c r="AE19" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF19" s="10">
         <v>0</v>
@@ -5177,17 +5177,17 @@
       <c r="AG19" s="14">
         <v>1</v>
       </c>
-      <c r="AH19" s="43" t="s">
+      <c r="AH19" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="AI19" s="42">
+      <c r="AI19" s="39">
         <v>3</v>
       </c>
       <c r="AJ19" s="10">
         <v>3</v>
       </c>
       <c r="AK19" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL19" s="10">
         <v>0</v>
@@ -5195,35 +5195,35 @@
       <c r="AM19" s="14">
         <v>1</v>
       </c>
-      <c r="AN19" s="43" t="s">
+      <c r="AN19" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="AO19" s="42">
-        <v>3</v>
+      <c r="AO19" s="39">
+        <v>0</v>
       </c>
       <c r="AP19" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ19" s="10">
         <v>0</v>
       </c>
       <c r="AR19" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS19" s="14">
         <v>0</v>
       </c>
-      <c r="AT19" s="44" t="s">
+      <c r="AT19" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU19" s="42">
+      <c r="AU19" s="39">
         <v>3</v>
       </c>
       <c r="AV19" s="10">
         <v>3</v>
       </c>
       <c r="AW19" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX19" s="10">
         <v>0</v>
@@ -5231,68 +5231,68 @@
       <c r="AY19" s="14">
         <v>1</v>
       </c>
-      <c r="AZ19" s="43" t="s">
+      <c r="AZ19" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="BA19" s="42">
-        <v>3</v>
+      <c r="BA19" s="39">
+        <v>0</v>
       </c>
       <c r="BB19" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC19" s="10">
         <v>0</v>
       </c>
       <c r="BD19" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BE19" s="14">
         <v>0</v>
       </c>
-      <c r="BF19" s="44" t="s">
+      <c r="BF19" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG19" s="45">
-        <v>3</v>
+      <c r="BG19" s="42">
+        <v>0</v>
       </c>
       <c r="BH19" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI19" s="10">
         <v>0</v>
       </c>
       <c r="BJ19" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK19" s="14">
         <v>0</v>
       </c>
-      <c r="BL19" s="47" t="s">
+      <c r="BL19" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM19" s="30">
+      <c r="BM19" s="27">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="20" spans="2:65" ht="135" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:65" ht="90" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C20" s="3">
         <v>6</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D20" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="39">
         <v>6</v>
       </c>
       <c r="F20" s="10">
         <v>6</v>
       </c>
       <c r="G20" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H20" s="10">
         <v>0</v>
@@ -5300,17 +5300,17 @@
       <c r="I20" s="14">
         <v>1</v>
       </c>
-      <c r="J20" s="43" t="s">
+      <c r="J20" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="42">
+      <c r="K20" s="39">
         <v>6</v>
       </c>
       <c r="L20" s="10">
         <v>6</v>
       </c>
       <c r="M20" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N20" s="10">
         <v>0</v>
@@ -5318,17 +5318,17 @@
       <c r="O20" s="14">
         <v>1</v>
       </c>
-      <c r="P20" s="43" t="s">
+      <c r="P20" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="Q20" s="42">
+      <c r="Q20" s="39">
         <v>6</v>
       </c>
       <c r="R20" s="10">
         <v>6</v>
       </c>
       <c r="S20" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T20" s="10">
         <v>0</v>
@@ -5336,17 +5336,17 @@
       <c r="U20" s="14">
         <v>1</v>
       </c>
-      <c r="V20" s="43" t="s">
+      <c r="V20" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="W20" s="42">
+      <c r="W20" s="39">
         <v>6</v>
       </c>
       <c r="X20" s="10">
         <v>6</v>
       </c>
       <c r="Y20" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="10">
         <v>0</v>
@@ -5354,17 +5354,17 @@
       <c r="AA20" s="14">
         <v>1</v>
       </c>
-      <c r="AB20" s="43" t="s">
+      <c r="AB20" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="AC20" s="42">
+      <c r="AC20" s="39">
         <v>6</v>
       </c>
       <c r="AD20" s="10">
         <v>6</v>
       </c>
       <c r="AE20" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="10">
         <v>0</v>
@@ -5372,17 +5372,17 @@
       <c r="AG20" s="14">
         <v>1</v>
       </c>
-      <c r="AH20" s="43" t="s">
+      <c r="AH20" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="AI20" s="42">
+      <c r="AI20" s="39">
         <v>6</v>
       </c>
       <c r="AJ20" s="10">
         <v>6</v>
       </c>
       <c r="AK20" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AL20" s="10">
         <v>0</v>
@@ -5390,35 +5390,35 @@
       <c r="AM20" s="14">
         <v>1</v>
       </c>
-      <c r="AN20" s="43" t="s">
+      <c r="AN20" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="AO20" s="42">
-        <v>6</v>
+      <c r="AO20" s="39">
+        <v>0</v>
       </c>
       <c r="AP20" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ20" s="10">
         <v>0</v>
       </c>
       <c r="AR20" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AS20" s="14">
         <v>0</v>
       </c>
-      <c r="AT20" s="44" t="s">
+      <c r="AT20" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU20" s="42">
+      <c r="AU20" s="39">
         <v>6</v>
       </c>
       <c r="AV20" s="10">
         <v>6</v>
       </c>
       <c r="AW20" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AX20" s="10">
         <v>0</v>
@@ -5426,68 +5426,68 @@
       <c r="AY20" s="14">
         <v>1</v>
       </c>
-      <c r="AZ20" s="43" t="s">
+      <c r="AZ20" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="BA20" s="42">
-        <v>6</v>
+      <c r="BA20" s="39">
+        <v>0</v>
       </c>
       <c r="BB20" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC20" s="10">
         <v>0</v>
       </c>
       <c r="BD20" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BE20" s="14">
         <v>0</v>
       </c>
-      <c r="BF20" s="44" t="s">
+      <c r="BF20" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG20" s="45">
-        <v>6</v>
+      <c r="BG20" s="42">
+        <v>0</v>
       </c>
       <c r="BH20" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI20" s="10">
         <v>0</v>
       </c>
       <c r="BJ20" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BK20" s="14">
         <v>0</v>
       </c>
-      <c r="BL20" s="47" t="s">
+      <c r="BL20" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM20" s="30">
+      <c r="BM20" s="27">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="21" spans="2:65" ht="180" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:65" ht="90" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C21" s="3">
         <v>6</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="42">
+      <c r="E21" s="39">
         <v>6</v>
       </c>
       <c r="F21" s="10">
         <v>6</v>
       </c>
       <c r="G21" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H21" s="10">
         <v>0</v>
@@ -5495,17 +5495,17 @@
       <c r="I21" s="14">
         <v>1</v>
       </c>
-      <c r="J21" s="43" t="s">
+      <c r="J21" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="K21" s="42">
+      <c r="K21" s="39">
         <v>6</v>
       </c>
       <c r="L21" s="10">
         <v>6</v>
       </c>
       <c r="M21" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N21" s="10">
         <v>0</v>
@@ -5513,17 +5513,17 @@
       <c r="O21" s="14">
         <v>1</v>
       </c>
-      <c r="P21" s="43" t="s">
+      <c r="P21" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="Q21" s="42">
+      <c r="Q21" s="39">
         <v>6</v>
       </c>
       <c r="R21" s="10">
         <v>6</v>
       </c>
       <c r="S21" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T21" s="10">
         <v>0</v>
@@ -5531,17 +5531,17 @@
       <c r="U21" s="14">
         <v>1</v>
       </c>
-      <c r="V21" s="43" t="s">
+      <c r="V21" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="W21" s="42">
+      <c r="W21" s="39">
         <v>6</v>
       </c>
       <c r="X21" s="10">
         <v>6</v>
       </c>
       <c r="Y21" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="10">
         <v>0</v>
@@ -5549,17 +5549,17 @@
       <c r="AA21" s="14">
         <v>1</v>
       </c>
-      <c r="AB21" s="43" t="s">
+      <c r="AB21" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="AC21" s="42">
+      <c r="AC21" s="39">
         <v>6</v>
       </c>
       <c r="AD21" s="10">
         <v>6</v>
       </c>
       <c r="AE21" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF21" s="10">
         <v>0</v>
@@ -5567,17 +5567,17 @@
       <c r="AG21" s="14">
         <v>1</v>
       </c>
-      <c r="AH21" s="43" t="s">
+      <c r="AH21" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="AI21" s="42">
+      <c r="AI21" s="39">
         <v>6</v>
       </c>
       <c r="AJ21" s="10">
         <v>6</v>
       </c>
       <c r="AK21" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AL21" s="10">
         <v>0</v>
@@ -5585,35 +5585,35 @@
       <c r="AM21" s="14">
         <v>1</v>
       </c>
-      <c r="AN21" s="43" t="s">
+      <c r="AN21" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="AO21" s="42">
-        <v>6</v>
+      <c r="AO21" s="39">
+        <v>0</v>
       </c>
       <c r="AP21" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ21" s="10">
         <v>0</v>
       </c>
       <c r="AR21" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AS21" s="14">
         <v>0</v>
       </c>
-      <c r="AT21" s="44" t="s">
+      <c r="AT21" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU21" s="42">
+      <c r="AU21" s="39">
         <v>6</v>
       </c>
       <c r="AV21" s="10">
         <v>6</v>
       </c>
       <c r="AW21" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AX21" s="10">
         <v>0</v>
@@ -5621,68 +5621,68 @@
       <c r="AY21" s="14">
         <v>1</v>
       </c>
-      <c r="AZ21" s="43" t="s">
+      <c r="AZ21" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="BA21" s="42">
-        <v>6</v>
+      <c r="BA21" s="39">
+        <v>0</v>
       </c>
       <c r="BB21" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC21" s="10">
         <v>0</v>
       </c>
       <c r="BD21" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BE21" s="14">
         <v>0</v>
       </c>
-      <c r="BF21" s="44" t="s">
+      <c r="BF21" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG21" s="45">
-        <v>6</v>
+      <c r="BG21" s="42">
+        <v>0</v>
       </c>
       <c r="BH21" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="10">
         <v>0</v>
       </c>
       <c r="BJ21" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BK21" s="14">
         <v>0</v>
       </c>
-      <c r="BL21" s="47" t="s">
+      <c r="BL21" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM21" s="30">
+      <c r="BM21" s="27">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="2:65" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:65" ht="45" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C22" s="3">
         <v>3</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D22" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="42">
+      <c r="E22" s="39">
         <v>3</v>
       </c>
       <c r="F22" s="10">
         <v>3</v>
       </c>
       <c r="G22" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H22" s="10">
         <v>0</v>
@@ -5690,17 +5690,17 @@
       <c r="I22" s="14">
         <v>1</v>
       </c>
-      <c r="J22" s="43" t="s">
+      <c r="J22" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="K22" s="42">
+      <c r="K22" s="39">
         <v>3</v>
       </c>
       <c r="L22" s="10">
         <v>3</v>
       </c>
       <c r="M22" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N22" s="10">
         <v>0</v>
@@ -5708,17 +5708,17 @@
       <c r="O22" s="14">
         <v>1</v>
       </c>
-      <c r="P22" s="43" t="s">
+      <c r="P22" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="Q22" s="42">
+      <c r="Q22" s="39">
         <v>3</v>
       </c>
       <c r="R22" s="10">
         <v>3</v>
       </c>
       <c r="S22" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T22" s="10">
         <v>0</v>
@@ -5726,17 +5726,17 @@
       <c r="U22" s="14">
         <v>1</v>
       </c>
-      <c r="V22" s="43" t="s">
+      <c r="V22" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="W22" s="42">
+      <c r="W22" s="39">
         <v>3</v>
       </c>
       <c r="X22" s="10">
         <v>3</v>
       </c>
       <c r="Y22" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="10">
         <v>0</v>
@@ -5744,17 +5744,17 @@
       <c r="AA22" s="14">
         <v>1</v>
       </c>
-      <c r="AB22" s="43" t="s">
+      <c r="AB22" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="AC22" s="42">
+      <c r="AC22" s="39">
         <v>3</v>
       </c>
       <c r="AD22" s="10">
         <v>3</v>
       </c>
       <c r="AE22" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF22" s="10">
         <v>0</v>
@@ -5762,17 +5762,17 @@
       <c r="AG22" s="14">
         <v>1</v>
       </c>
-      <c r="AH22" s="43" t="s">
+      <c r="AH22" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="AI22" s="42">
+      <c r="AI22" s="39">
         <v>3</v>
       </c>
       <c r="AJ22" s="10">
         <v>3</v>
       </c>
       <c r="AK22" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL22" s="10">
         <v>0</v>
@@ -5780,35 +5780,35 @@
       <c r="AM22" s="14">
         <v>1</v>
       </c>
-      <c r="AN22" s="43" t="s">
+      <c r="AN22" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="AO22" s="42">
-        <v>3</v>
+      <c r="AO22" s="39">
+        <v>1</v>
       </c>
       <c r="AP22" s="10">
         <v>1</v>
       </c>
       <c r="AQ22" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR22" s="10">
-        <v>0</v>
-      </c>
-      <c r="AS22" s="48">
+        <v>2</v>
+      </c>
+      <c r="AS22" s="45">
         <v>0.33333333333333298</v>
       </c>
-      <c r="AT22" s="44" t="s">
+      <c r="AT22" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="AU22" s="42">
+      <c r="AU22" s="39">
         <v>3</v>
       </c>
       <c r="AV22" s="10">
         <v>3</v>
       </c>
       <c r="AW22" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX22" s="10">
         <v>0</v>
@@ -5816,35 +5816,35 @@
       <c r="AY22" s="14">
         <v>1</v>
       </c>
-      <c r="AZ22" s="43" t="s">
+      <c r="AZ22" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="BA22" s="42">
-        <v>3</v>
+      <c r="BA22" s="39">
+        <v>1</v>
       </c>
       <c r="BB22" s="10">
         <v>1</v>
       </c>
       <c r="BC22" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD22" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE22" s="48">
+        <v>2</v>
+      </c>
+      <c r="BE22" s="45">
         <v>0.33333333333333298</v>
       </c>
-      <c r="BF22" s="44" t="s">
+      <c r="BF22" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="BG22" s="45">
+      <c r="BG22" s="42">
         <v>3</v>
       </c>
       <c r="BH22" s="10">
         <v>3</v>
       </c>
       <c r="BI22" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ22" s="10">
         <v>0</v>
@@ -5852,32 +5852,32 @@
       <c r="BK22" s="14">
         <v>1</v>
       </c>
-      <c r="BL22" s="46" t="s">
+      <c r="BL22" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="BM22" s="30">
+      <c r="BM22" s="27">
         <f t="shared" si="0"/>
         <v>0.86666666666666659</v>
       </c>
     </row>
-    <row r="23" spans="2:65" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:65" ht="45" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C23" s="3">
         <v>3</v>
       </c>
-      <c r="D23" s="33" t="s">
+      <c r="D23" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="42">
+      <c r="E23" s="39">
         <v>3</v>
       </c>
       <c r="F23" s="10">
         <v>3</v>
       </c>
       <c r="G23" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" s="10">
         <v>0</v>
@@ -5885,17 +5885,17 @@
       <c r="I23" s="14">
         <v>1</v>
       </c>
-      <c r="J23" s="43" t="s">
+      <c r="J23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="K23" s="42">
+      <c r="K23" s="39">
         <v>3</v>
       </c>
       <c r="L23" s="10">
         <v>3</v>
       </c>
       <c r="M23" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N23" s="10">
         <v>0</v>
@@ -5903,17 +5903,17 @@
       <c r="O23" s="14">
         <v>1</v>
       </c>
-      <c r="P23" s="43" t="s">
+      <c r="P23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="Q23" s="42">
+      <c r="Q23" s="39">
         <v>3</v>
       </c>
       <c r="R23" s="10">
         <v>3</v>
       </c>
       <c r="S23" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
@@ -5921,17 +5921,17 @@
       <c r="U23" s="14">
         <v>1</v>
       </c>
-      <c r="V23" s="43" t="s">
+      <c r="V23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="W23" s="42">
+      <c r="W23" s="39">
         <v>3</v>
       </c>
       <c r="X23" s="10">
         <v>3</v>
       </c>
       <c r="Y23" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="10">
         <v>0</v>
@@ -5939,17 +5939,17 @@
       <c r="AA23" s="14">
         <v>1</v>
       </c>
-      <c r="AB23" s="43" t="s">
+      <c r="AB23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="AC23" s="42">
+      <c r="AC23" s="39">
         <v>3</v>
       </c>
       <c r="AD23" s="10">
         <v>3</v>
       </c>
       <c r="AE23" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF23" s="10">
         <v>0</v>
@@ -5957,17 +5957,17 @@
       <c r="AG23" s="14">
         <v>1</v>
       </c>
-      <c r="AH23" s="43" t="s">
+      <c r="AH23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="AI23" s="42">
+      <c r="AI23" s="39">
         <v>3</v>
       </c>
       <c r="AJ23" s="10">
         <v>3</v>
       </c>
       <c r="AK23" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL23" s="10">
         <v>0</v>
@@ -5975,35 +5975,35 @@
       <c r="AM23" s="14">
         <v>1</v>
       </c>
-      <c r="AN23" s="43" t="s">
+      <c r="AN23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="AO23" s="42">
-        <v>3</v>
+      <c r="AO23" s="39">
+        <v>0</v>
       </c>
       <c r="AP23" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ23" s="10">
         <v>0</v>
       </c>
       <c r="AR23" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS23" s="14">
         <v>0</v>
       </c>
-      <c r="AT23" s="44" t="s">
+      <c r="AT23" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU23" s="42">
+      <c r="AU23" s="39">
         <v>3</v>
       </c>
       <c r="AV23" s="10">
         <v>3</v>
       </c>
       <c r="AW23" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX23" s="10">
         <v>0</v>
@@ -6011,35 +6011,35 @@
       <c r="AY23" s="14">
         <v>1</v>
       </c>
-      <c r="AZ23" s="43" t="s">
+      <c r="AZ23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="BA23" s="42">
-        <v>3</v>
+      <c r="BA23" s="39">
+        <v>0</v>
       </c>
       <c r="BB23" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC23" s="10">
         <v>0</v>
       </c>
       <c r="BD23" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BE23" s="14">
         <v>0</v>
       </c>
-      <c r="BF23" s="44" t="s">
+      <c r="BF23" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG23" s="45">
+      <c r="BG23" s="42">
         <v>3</v>
       </c>
       <c r="BH23" s="10">
         <v>3</v>
       </c>
       <c r="BI23" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ23" s="10">
         <v>0</v>
@@ -6047,10 +6047,10 @@
       <c r="BK23" s="14">
         <v>1</v>
       </c>
-      <c r="BL23" s="46" t="s">
+      <c r="BL23" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="BM23" s="30">
+      <c r="BM23" s="27">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
@@ -6062,17 +6062,17 @@
       <c r="C24" s="3">
         <v>1</v>
       </c>
-      <c r="D24" s="33" t="s">
+      <c r="D24" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="42">
+      <c r="E24" s="39">
         <v>1</v>
       </c>
       <c r="F24" s="10">
         <v>1</v>
       </c>
       <c r="G24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="10">
         <v>0</v>
@@ -6080,17 +6080,17 @@
       <c r="I24" s="14">
         <v>1</v>
       </c>
-      <c r="J24" s="44" t="s">
+      <c r="J24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="K24" s="42">
+      <c r="K24" s="39">
         <v>1</v>
       </c>
       <c r="L24" s="10">
         <v>1</v>
       </c>
       <c r="M24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="10">
         <v>0</v>
@@ -6098,17 +6098,17 @@
       <c r="O24" s="14">
         <v>1</v>
       </c>
-      <c r="P24" s="44" t="s">
+      <c r="P24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="42">
+      <c r="Q24" s="39">
         <v>1</v>
       </c>
       <c r="R24" s="10">
         <v>1</v>
       </c>
       <c r="S24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" s="10">
         <v>0</v>
@@ -6116,17 +6116,17 @@
       <c r="U24" s="14">
         <v>1</v>
       </c>
-      <c r="V24" s="44" t="s">
+      <c r="V24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="W24" s="42">
+      <c r="W24" s="39">
         <v>1</v>
       </c>
       <c r="X24" s="10">
         <v>1</v>
       </c>
       <c r="Y24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="10">
         <v>0</v>
@@ -6134,17 +6134,17 @@
       <c r="AA24" s="14">
         <v>1</v>
       </c>
-      <c r="AB24" s="44" t="s">
+      <c r="AB24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="AC24" s="42">
+      <c r="AC24" s="39">
         <v>1</v>
       </c>
       <c r="AD24" s="10">
         <v>1</v>
       </c>
       <c r="AE24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF24" s="10">
         <v>0</v>
@@ -6152,17 +6152,17 @@
       <c r="AG24" s="14">
         <v>1</v>
       </c>
-      <c r="AH24" s="44" t="s">
+      <c r="AH24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="AI24" s="42">
+      <c r="AI24" s="39">
         <v>1</v>
       </c>
       <c r="AJ24" s="10">
         <v>1</v>
       </c>
       <c r="AK24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL24" s="10">
         <v>0</v>
@@ -6170,14 +6170,14 @@
       <c r="AM24" s="14">
         <v>1</v>
       </c>
-      <c r="AN24" s="44" t="s">
+      <c r="AN24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="AO24" s="42">
-        <v>1</v>
+      <c r="AO24" s="39">
+        <v>0</v>
       </c>
       <c r="AP24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ24" s="10">
         <v>0</v>
@@ -6188,17 +6188,17 @@
       <c r="AS24" s="14">
         <v>0</v>
       </c>
-      <c r="AT24" s="44" t="s">
+      <c r="AT24" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU24" s="42">
+      <c r="AU24" s="39">
         <v>1</v>
       </c>
       <c r="AV24" s="10">
         <v>1</v>
       </c>
       <c r="AW24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX24" s="10">
         <v>0</v>
@@ -6206,14 +6206,14 @@
       <c r="AY24" s="14">
         <v>1</v>
       </c>
-      <c r="AZ24" s="44" t="s">
+      <c r="AZ24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="BA24" s="42">
-        <v>1</v>
+      <c r="BA24" s="39">
+        <v>0</v>
       </c>
       <c r="BB24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC24" s="10">
         <v>0</v>
@@ -6224,14 +6224,14 @@
       <c r="BE24" s="14">
         <v>0</v>
       </c>
-      <c r="BF24" s="44" t="s">
+      <c r="BF24" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG24" s="45">
-        <v>1</v>
+      <c r="BG24" s="42">
+        <v>0</v>
       </c>
       <c r="BH24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI24" s="10">
         <v>0</v>
@@ -6242,10 +6242,10 @@
       <c r="BK24" s="14">
         <v>0</v>
       </c>
-      <c r="BL24" s="47" t="s">
+      <c r="BL24" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM24" s="30">
+      <c r="BM24" s="27">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
@@ -6257,14 +6257,14 @@
       <c r="C25" s="7">
         <v>1</v>
       </c>
-      <c r="D25" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E25" s="42">
-        <v>1</v>
+      <c r="D25" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E25" s="39">
+        <v>0</v>
       </c>
       <c r="F25" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="10">
         <v>0</v>
@@ -6275,12 +6275,12 @@
       <c r="I25" s="14">
         <v>0</v>
       </c>
-      <c r="J25" s="44"/>
-      <c r="K25" s="42">
-        <v>1</v>
+      <c r="J25" s="41"/>
+      <c r="K25" s="39">
+        <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
@@ -6291,12 +6291,12 @@
       <c r="O25" s="14">
         <v>0</v>
       </c>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="42">
-        <v>1</v>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="39">
+        <v>0</v>
       </c>
       <c r="R25" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" s="10">
         <v>0</v>
@@ -6307,12 +6307,12 @@
       <c r="U25" s="14">
         <v>0</v>
       </c>
-      <c r="V25" s="44"/>
-      <c r="W25" s="42">
-        <v>1</v>
+      <c r="V25" s="41"/>
+      <c r="W25" s="39">
+        <v>0</v>
       </c>
       <c r="X25" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="10">
         <v>0</v>
@@ -6323,12 +6323,12 @@
       <c r="AA25" s="14">
         <v>0</v>
       </c>
-      <c r="AB25" s="44"/>
-      <c r="AC25" s="42">
-        <v>1</v>
+      <c r="AB25" s="41"/>
+      <c r="AC25" s="39">
+        <v>0</v>
       </c>
       <c r="AD25" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE25" s="10">
         <v>0</v>
@@ -6339,12 +6339,12 @@
       <c r="AG25" s="14">
         <v>0</v>
       </c>
-      <c r="AH25" s="44"/>
-      <c r="AI25" s="42">
-        <v>1</v>
+      <c r="AH25" s="41"/>
+      <c r="AI25" s="39">
+        <v>0</v>
       </c>
       <c r="AJ25" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="10">
         <v>0</v>
@@ -6355,12 +6355,12 @@
       <c r="AM25" s="14">
         <v>0</v>
       </c>
-      <c r="AN25" s="44"/>
-      <c r="AO25" s="42">
-        <v>1</v>
+      <c r="AN25" s="41"/>
+      <c r="AO25" s="39">
+        <v>0</v>
       </c>
       <c r="AP25" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ25" s="10">
         <v>0</v>
@@ -6371,14 +6371,14 @@
       <c r="AS25" s="14">
         <v>0</v>
       </c>
-      <c r="AT25" s="44" t="s">
+      <c r="AT25" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AU25" s="42">
-        <v>1</v>
+      <c r="AU25" s="39">
+        <v>0</v>
       </c>
       <c r="AV25" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW25" s="10">
         <v>0</v>
@@ -6389,12 +6389,12 @@
       <c r="AY25" s="14">
         <v>0</v>
       </c>
-      <c r="AZ25" s="44"/>
-      <c r="BA25" s="42">
-        <v>1</v>
+      <c r="AZ25" s="41"/>
+      <c r="BA25" s="39">
+        <v>0</v>
       </c>
       <c r="BB25" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC25" s="10">
         <v>0</v>
@@ -6405,14 +6405,14 @@
       <c r="BE25" s="14">
         <v>0</v>
       </c>
-      <c r="BF25" s="44" t="s">
+      <c r="BF25" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="BG25" s="45">
-        <v>1</v>
+      <c r="BG25" s="42">
+        <v>0</v>
       </c>
       <c r="BH25" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI25" s="10">
         <v>0</v>
@@ -6423,10 +6423,10 @@
       <c r="BK25" s="14">
         <v>0</v>
       </c>
-      <c r="BL25" s="47" t="s">
+      <c r="BL25" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BM25" s="30">
+      <c r="BM25" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6438,17 +6438,17 @@
       <c r="C26" s="5">
         <v>1</v>
       </c>
-      <c r="D26" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="49">
+      <c r="D26" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="46">
         <v>1</v>
       </c>
       <c r="F26" s="15">
         <v>1</v>
       </c>
       <c r="G26" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="15">
         <v>0</v>
@@ -6456,17 +6456,17 @@
       <c r="I26" s="16">
         <v>1</v>
       </c>
-      <c r="J26" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K26" s="49">
+      <c r="J26" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K26" s="46">
         <v>1</v>
       </c>
       <c r="L26" s="15">
         <v>1</v>
       </c>
       <c r="M26" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="15">
         <v>0</v>
@@ -6474,17 +6474,17 @@
       <c r="O26" s="16">
         <v>1</v>
       </c>
-      <c r="P26" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="49">
+      <c r="P26" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="46">
         <v>1</v>
       </c>
       <c r="R26" s="15">
         <v>1</v>
       </c>
       <c r="S26" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" s="15">
         <v>0</v>
@@ -6492,17 +6492,17 @@
       <c r="U26" s="16">
         <v>1</v>
       </c>
-      <c r="V26" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="W26" s="49">
+      <c r="V26" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="W26" s="46">
         <v>1</v>
       </c>
       <c r="X26" s="15">
         <v>1</v>
       </c>
       <c r="Y26" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="15">
         <v>0</v>
@@ -6510,17 +6510,17 @@
       <c r="AA26" s="16">
         <v>1</v>
       </c>
-      <c r="AB26" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="49">
+      <c r="AB26" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="46">
         <v>1</v>
       </c>
       <c r="AD26" s="15">
         <v>1</v>
       </c>
       <c r="AE26" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="15">
         <v>0</v>
@@ -6528,17 +6528,17 @@
       <c r="AG26" s="16">
         <v>1</v>
       </c>
-      <c r="AH26" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI26" s="49">
+      <c r="AH26" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI26" s="46">
         <v>1</v>
       </c>
       <c r="AJ26" s="15">
         <v>1</v>
       </c>
       <c r="AK26" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL26" s="15">
         <v>0</v>
@@ -6546,17 +6546,17 @@
       <c r="AM26" s="16">
         <v>1</v>
       </c>
-      <c r="AN26" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO26" s="49">
+      <c r="AN26" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO26" s="46">
         <v>1</v>
       </c>
       <c r="AP26" s="15">
         <v>1</v>
       </c>
       <c r="AQ26" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR26" s="15">
         <v>0</v>
@@ -6564,17 +6564,17 @@
       <c r="AS26" s="16">
         <v>1</v>
       </c>
-      <c r="AT26" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="AU26" s="49">
+      <c r="AT26" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU26" s="46">
         <v>1</v>
       </c>
       <c r="AV26" s="15">
         <v>1</v>
       </c>
       <c r="AW26" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX26" s="15">
         <v>0</v>
@@ -6582,17 +6582,17 @@
       <c r="AY26" s="16">
         <v>1</v>
       </c>
-      <c r="AZ26" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="BA26" s="49">
+      <c r="AZ26" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA26" s="46">
         <v>1</v>
       </c>
       <c r="BB26" s="15">
         <v>1</v>
       </c>
       <c r="BC26" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD26" s="15">
         <v>0</v>
@@ -6600,14 +6600,14 @@
       <c r="BE26" s="16">
         <v>1</v>
       </c>
-      <c r="BF26" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG26" s="51">
-        <v>1</v>
+      <c r="BF26" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="BG26" s="48">
+        <v>0</v>
       </c>
       <c r="BH26" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI26" s="15">
         <v>0</v>
@@ -6618,36 +6618,36 @@
       <c r="BK26" s="16">
         <v>0</v>
       </c>
-      <c r="BL26" s="52" t="s">
+      <c r="BL26" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="BM26" s="53">
+      <c r="BM26" s="50">
         <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
     </row>
     <row r="27" spans="2:65" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BL27" s="54" t="s">
+      <c r="BL27" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="BM27" s="55">
+      <c r="BM27" s="52">
         <f>AVERAGE(BM4:BM26)</f>
         <v>0.69565217391304335</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:J2"/>
-    <mergeCell ref="K2:P2"/>
-    <mergeCell ref="Q2:V2"/>
-    <mergeCell ref="W2:AB2"/>
     <mergeCell ref="BG2:BL2"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AI2:AN2"/>
     <mergeCell ref="AO2:AT2"/>
     <mergeCell ref="AU2:AZ2"/>
     <mergeCell ref="BA2:BF2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="K2:P2"/>
+    <mergeCell ref="Q2:V2"/>
+    <mergeCell ref="W2:AB2"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="I1:I1048576 U2 AG2 AS2 BE2">
@@ -6794,8 +6794,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM27">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="BM4:BM27">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6806,8 +6806,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM4:BM27">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="BM27">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6824,20 +6824,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="58f62c55-904c-45ab-921a-aadd23c9ae33" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="58f62c55-904c-45ab-921a-aadd23c9ae33" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7082,6 +7082,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDD6D5E5-ECB9-438E-99E0-1D766706DDC6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB0BEC68-A8D2-41C9-8F24-363FE6B4FCA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="f146318e-9396-49ea-b06c-cd0efdf32951"/>
@@ -7094,14 +7102,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="58f62c55-904c-45ab-921a-aadd23c9ae33"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDD6D5E5-ECB9-438E-99E0-1D766706DDC6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
